--- a/data/availability/projects/sodic/westown-medical-centre.xlsx
+++ b/data/availability/projects/sodic/westown-medical-centre.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,63 +1520,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>westown-medical-centre</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Ready / 2027</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
